--- a/Team-Data/2013-14/10-31-2013-14.xlsx
+++ b/Team-Data/2013-14/10-31-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,16 +806,16 @@
         <v>-9</v>
       </c>
       <c r="AD2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG2" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH2" t="n">
         <v>3</v>
@@ -757,16 +824,16 @@
         <v>14</v>
       </c>
       <c r="AJ2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AL2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN2" t="n">
         <v>18</v>
@@ -775,16 +842,16 @@
         <v>3</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
         <v>28</v>
       </c>
       <c r="AS2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
         <v>28</v>
@@ -793,7 +860,7 @@
         <v>4</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW2" t="n">
         <v>1</v>
@@ -805,16 +872,16 @@
         <v>2</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA2" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC2" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -921,16 +988,16 @@
         <v>-6</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF3" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG3" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH3" t="n">
         <v>3</v>
@@ -942,28 +1009,28 @@
         <v>30</v>
       </c>
       <c r="AK3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AN3" t="n">
         <v>28</v>
       </c>
-      <c r="AN3" t="n">
-        <v>29</v>
-      </c>
       <c r="AO3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AP3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ3" t="n">
         <v>21</v>
       </c>
       <c r="AR3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS3" t="n">
         <v>27</v>
@@ -975,28 +1042,28 @@
         <v>26</v>
       </c>
       <c r="AV3" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
         <v>23</v>
       </c>
       <c r="BA3" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BB3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC3" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BD3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -1103,25 +1170,25 @@
         <v>-4</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE4" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF4" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>13</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>11</v>
       </c>
       <c r="AK4" t="n">
         <v>28</v>
@@ -1130,28 +1197,28 @@
         <v>8</v>
       </c>
       <c r="AM4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AS4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT4" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU4" t="n">
         <v>9</v>
@@ -1160,10 +1227,10 @@
         <v>7</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
         <v>4</v>
@@ -1172,13 +1239,13 @@
         <v>23</v>
       </c>
       <c r="BA4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB4" t="n">
         <v>20</v>
       </c>
-      <c r="BB4" t="n">
-        <v>19</v>
-      </c>
       <c r="BC4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -1285,22 +1352,22 @@
         <v>-13</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
       </c>
       <c r="AI5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1309,7 +1376,7 @@
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM5" t="n">
         <v>30</v>
@@ -1327,13 +1394,13 @@
         <v>24</v>
       </c>
       <c r="AR5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS5" t="n">
         <v>29</v>
       </c>
       <c r="AT5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU5" t="n">
         <v>28</v>
@@ -1342,13 +1409,13 @@
         <v>1</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
       </c>
       <c r="AY5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ5" t="n">
         <v>11</v>
@@ -1360,7 +1427,7 @@
         <v>29</v>
       </c>
       <c r="BC5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -1389,160 +1456,160 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J6" t="n">
-        <v>79.5</v>
+        <v>83</v>
       </c>
       <c r="K6" t="n">
-        <v>0.415</v>
+        <v>0.422</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="N6" t="n">
-        <v>0.238</v>
+        <v>0.269</v>
       </c>
       <c r="O6" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="P6" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.833</v>
+        <v>0.783</v>
       </c>
       <c r="R6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="S6" t="n">
-        <v>32.5</v>
+        <v>30</v>
       </c>
       <c r="T6" t="n">
-        <v>44.5</v>
+        <v>41</v>
       </c>
       <c r="U6" t="n">
-        <v>21.5</v>
+        <v>23</v>
       </c>
       <c r="V6" t="n">
         <v>19</v>
       </c>
       <c r="W6" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="X6" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="Y6" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.5</v>
+        <v>27</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.5</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>88.5</v>
+        <v>95</v>
       </c>
       <c r="AC6" t="n">
-        <v>-5.5</v>
+        <v>-12</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE6" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AF6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>27</v>
+      </c>
+      <c r="AO6" t="n">
         <v>13</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AP6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU6" t="n">
         <v>13</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>23</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>22</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>15</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>3</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>14</v>
       </c>
       <c r="AV6" t="n">
         <v>20</v>
       </c>
       <c r="AW6" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AX6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ6" t="n">
         <v>23</v>
       </c>
-      <c r="AY6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>14</v>
-      </c>
       <c r="BA6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="BB6" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="BC6" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4</v>
       </c>
       <c r="AD7" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE7" t="n">
         <v>2</v>
@@ -1664,19 +1731,19 @@
         <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AJ7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL7" t="n">
         <v>22</v>
       </c>
       <c r="AM7" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN7" t="n">
         <v>18</v>
@@ -1685,7 +1752,7 @@
         <v>7</v>
       </c>
       <c r="AP7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ7" t="n">
         <v>22</v>
@@ -1715,16 +1782,16 @@
         <v>27</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BA7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB7" t="n">
         <v>15</v>
       </c>
       <c r="BC7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>9</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE8" t="n">
         <v>2</v>
@@ -1846,10 +1913,10 @@
         <v>3</v>
       </c>
       <c r="AI8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
         <v>1</v>
@@ -1858,31 +1925,31 @@
         <v>3</v>
       </c>
       <c r="AM8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN8" t="n">
         <v>5</v>
       </c>
       <c r="AO8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AP8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR8" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT8" t="n">
         <v>14</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV8" t="n">
         <v>26</v>
@@ -1894,13 +1961,13 @@
         <v>29</v>
       </c>
       <c r="AY8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB8" t="n">
         <v>3</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -2013,40 +2080,40 @@
         <v>-2</v>
       </c>
       <c r="AD9" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
         <v>3</v>
       </c>
       <c r="AI9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AJ9" t="n">
         <v>18</v>
       </c>
       <c r="AK9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL9" t="n">
         <v>22</v>
       </c>
       <c r="AM9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN9" t="n">
         <v>18</v>
       </c>
       <c r="AO9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP9" t="n">
         <v>25</v>
@@ -2055,13 +2122,13 @@
         <v>1</v>
       </c>
       <c r="AR9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU9" t="n">
         <v>17</v>
@@ -2082,13 +2149,13 @@
         <v>11</v>
       </c>
       <c r="BA9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BB9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>11</v>
       </c>
       <c r="AD10" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE10" t="n">
         <v>2</v>
@@ -2213,31 +2280,31 @@
         <v>10</v>
       </c>
       <c r="AJ10" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL10" t="n">
         <v>8</v>
       </c>
       <c r="AM10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO10" t="n">
         <v>4</v>
       </c>
       <c r="AP10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AS10" t="n">
         <v>13</v>
@@ -2267,10 +2334,10 @@
         <v>1</v>
       </c>
       <c r="BB10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -2299,160 +2366,160 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H11" t="n">
         <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J11" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="K11" t="n">
-        <v>0.531</v>
+        <v>0.535</v>
       </c>
       <c r="L11" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="M11" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.556</v>
       </c>
       <c r="O11" t="n">
-        <v>20.5</v>
+        <v>18</v>
       </c>
       <c r="P11" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.732</v>
+        <v>0.783</v>
       </c>
       <c r="R11" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="S11" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="T11" t="n">
-        <v>40.5</v>
+        <v>48</v>
       </c>
       <c r="U11" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="V11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="X11" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="n">
         <v>4</v>
       </c>
       <c r="Z11" t="n">
-        <v>28.5</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AB11" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="AC11" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="AD11" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
       </c>
       <c r="AF11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="n">
         <v>13</v>
       </c>
-      <c r="AG11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AJ11" t="n">
+      <c r="AP11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW11" t="n">
         <v>12</v>
       </c>
-      <c r="AK11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM11" t="n">
+      <c r="AX11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY11" t="n">
         <v>7</v>
       </c>
-      <c r="AN11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>17</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>18</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>2</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>16</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>8</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="BA11" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="BB11" t="n">
         <v>1</v>
       </c>
       <c r="BC11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>13</v>
       </c>
       <c r="AD12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>2</v>
@@ -2577,40 +2644,40 @@
         <v>15</v>
       </c>
       <c r="AJ12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL12" t="n">
         <v>8</v>
       </c>
       <c r="AM12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR12" t="n">
         <v>4</v>
       </c>
       <c r="AS12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT12" t="n">
         <v>1</v>
       </c>
       <c r="AU12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV12" t="n">
         <v>20</v>
@@ -2622,7 +2689,7 @@
         <v>7</v>
       </c>
       <c r="AY12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ12" t="n">
         <v>4</v>
@@ -2634,7 +2701,7 @@
         <v>17</v>
       </c>
       <c r="BC12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -2762,7 +2829,7 @@
         <v>29</v>
       </c>
       <c r="AK13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL13" t="n">
         <v>11</v>
@@ -2777,22 +2844,22 @@
         <v>6</v>
       </c>
       <c r="AP13" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR13" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AT13" t="n">
         <v>18</v>
       </c>
       <c r="AU13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV13" t="n">
         <v>24</v>
@@ -2804,13 +2871,13 @@
         <v>1</v>
       </c>
       <c r="AY13" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ13" t="n">
         <v>3</v>
       </c>
       <c r="BA13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB13" t="n">
         <v>17</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -2845,160 +2912,160 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>1</v>
       </c>
       <c r="G14" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>41.5</v>
+        <v>41</v>
       </c>
       <c r="J14" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K14" t="n">
         <v>0.494</v>
       </c>
       <c r="L14" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>24.5</v>
+        <v>21</v>
       </c>
       <c r="N14" t="n">
-        <v>0.347</v>
+        <v>0.381</v>
       </c>
       <c r="O14" t="n">
+        <v>13</v>
+      </c>
+      <c r="P14" t="n">
         <v>23</v>
       </c>
-      <c r="P14" t="n">
-        <v>36.5</v>
-      </c>
       <c r="Q14" t="n">
-        <v>0.63</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="S14" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T14" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="U14" t="n">
         <v>27</v>
       </c>
       <c r="V14" t="n">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="W14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="X14" t="n">
         <v>4</v>
       </c>
       <c r="Y14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Z14" t="n">
-        <v>25.5</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AB14" t="n">
-        <v>114.5</v>
+        <v>103</v>
       </c>
       <c r="AC14" t="n">
-        <v>-1</v>
+        <v>-13</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AF14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG14" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="AH14" t="n">
         <v>3</v>
       </c>
       <c r="AI14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM14" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="AN14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS14" t="n">
         <v>17</v>
       </c>
-      <c r="AO14" t="n">
-        <v>7</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>8</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>20</v>
-      </c>
       <c r="AT14" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AU14" t="n">
         <v>4</v>
       </c>
       <c r="AV14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX14" t="n">
         <v>19</v>
       </c>
       <c r="AY14" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AZ14" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="BB14" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="BC14" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -3111,10 +3178,10 @@
         <v>2</v>
       </c>
       <c r="AF15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH15" t="n">
         <v>3</v>
@@ -3138,10 +3205,10 @@
         <v>4</v>
       </c>
       <c r="AO15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ15" t="n">
         <v>20</v>
@@ -3153,13 +3220,13 @@
         <v>13</v>
       </c>
       <c r="AT15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU15" t="n">
         <v>15</v>
       </c>
       <c r="AV15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW15" t="n">
         <v>21</v>
@@ -3171,16 +3238,16 @@
         <v>23</v>
       </c>
       <c r="AZ15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA15" t="n">
         <v>17</v>
       </c>
       <c r="BB15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC15" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -3287,16 +3354,16 @@
         <v>-7</v>
       </c>
       <c r="AD16" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF16" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG16" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH16" t="n">
         <v>3</v>
@@ -3308,13 +3375,13 @@
         <v>3</v>
       </c>
       <c r="AK16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN16" t="n">
         <v>3</v>
@@ -3329,10 +3396,10 @@
         <v>29</v>
       </c>
       <c r="AR16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT16" t="n">
         <v>10</v>
@@ -3350,7 +3417,7 @@
         <v>25</v>
       </c>
       <c r="AY16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ16" t="n">
         <v>2</v>
@@ -3359,10 +3426,10 @@
         <v>23</v>
       </c>
       <c r="BB16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC16" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -3475,10 +3542,10 @@
         <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
         <v>3</v>
@@ -3490,10 +3557,10 @@
         <v>20</v>
       </c>
       <c r="AK17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM17" t="n">
         <v>1</v>
@@ -3502,22 +3569,22 @@
         <v>7</v>
       </c>
       <c r="AO17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP17" t="n">
+        <v>21</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>26</v>
+      </c>
+      <c r="AS17" t="n">
         <v>20</v>
       </c>
-      <c r="AQ17" t="n">
-        <v>14</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>19</v>
-      </c>
       <c r="AT17" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU17" t="n">
         <v>3</v>
@@ -3526,25 +3593,25 @@
         <v>24</v>
       </c>
       <c r="AW17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY17" t="n">
         <v>3</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BC17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -3651,37 +3718,37 @@
         <v>-7</v>
       </c>
       <c r="AD18" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF18" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>17</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK18" t="n">
         <v>13</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>18</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>12</v>
       </c>
       <c r="AL18" t="n">
         <v>22</v>
       </c>
       <c r="AM18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN18" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO18" t="n">
         <v>27</v>
@@ -3690,7 +3757,7 @@
         <v>30</v>
       </c>
       <c r="AQ18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR18" t="n">
         <v>28</v>
@@ -3708,13 +3775,13 @@
         <v>30</v>
       </c>
       <c r="AW18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX18" t="n">
         <v>19</v>
       </c>
       <c r="AY18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ18" t="n">
         <v>15</v>
@@ -3726,7 +3793,7 @@
         <v>29</v>
       </c>
       <c r="BC18" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>5</v>
       </c>
       <c r="AD19" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE19" t="n">
         <v>2</v>
@@ -3854,22 +3921,22 @@
         <v>1</v>
       </c>
       <c r="AK19" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN19" t="n">
         <v>21</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>22</v>
       </c>
       <c r="AO19" t="n">
         <v>2</v>
       </c>
       <c r="AP19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AQ19" t="n">
         <v>6</v>
@@ -3878,7 +3945,7 @@
         <v>4</v>
       </c>
       <c r="AS19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT19" t="n">
         <v>2</v>
@@ -3896,19 +3963,19 @@
         <v>25</v>
       </c>
       <c r="AY19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -4015,25 +4082,25 @@
         <v>-5</v>
       </c>
       <c r="AD20" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF20" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG20" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH20" t="n">
         <v>3</v>
       </c>
       <c r="AI20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK20" t="n">
         <v>29</v>
@@ -4048,10 +4115,10 @@
         <v>6</v>
       </c>
       <c r="AO20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ20" t="n">
         <v>7</v>
@@ -4060,13 +4127,13 @@
         <v>3</v>
       </c>
       <c r="AS20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT20" t="n">
         <v>13</v>
       </c>
       <c r="AU20" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
@@ -4087,10 +4154,10 @@
         <v>23</v>
       </c>
       <c r="BB20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC20" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -4119,160 +4186,160 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
         <v>48</v>
       </c>
       <c r="I21" t="n">
-        <v>33.5</v>
+        <v>36</v>
       </c>
       <c r="J21" t="n">
-        <v>78.5</v>
+        <v>71</v>
       </c>
       <c r="K21" t="n">
-        <v>0.427</v>
+        <v>0.507</v>
       </c>
       <c r="L21" t="n">
+        <v>3</v>
+      </c>
+      <c r="M21" t="n">
+        <v>13</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="O21" t="n">
+        <v>15</v>
+      </c>
+      <c r="P21" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="R21" t="n">
         <v>6</v>
       </c>
-      <c r="M21" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.324</v>
-      </c>
-      <c r="O21" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="P21" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.806</v>
-      </c>
-      <c r="R21" t="n">
-        <v>9.5</v>
-      </c>
       <c r="S21" t="n">
-        <v>28.5</v>
+        <v>28</v>
       </c>
       <c r="T21" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="U21" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="V21" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="W21" t="n">
         <v>12</v>
       </c>
       <c r="X21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>16</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>22</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>90</v>
+      </c>
+      <c r="AC21" t="n">
         <v>7</v>
       </c>
-      <c r="Y21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>85.5</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3</v>
-      </c>
       <c r="AD21" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AG21" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="AH21" t="n">
         <v>3</v>
       </c>
       <c r="AI21" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AJ21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>6</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO21" t="n">
         <v>20</v>
       </c>
-      <c r="AK21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>19</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AO21" t="n">
+      <c r="AP21" t="n">
         <v>25</v>
       </c>
-      <c r="AP21" t="n">
-        <v>27</v>
-      </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AR21" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AS21" t="n">
         <v>22</v>
       </c>
       <c r="AT21" t="n">
+        <v>27</v>
+      </c>
+      <c r="AU21" t="n">
         <v>23</v>
       </c>
-      <c r="AU21" t="n">
-        <v>21</v>
-      </c>
       <c r="AV21" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="AW21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX21" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY21" t="n">
         <v>7</v>
       </c>
       <c r="AZ21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA21" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="BB21" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="BC21" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>3</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4394,40 +4461,40 @@
         <v>3</v>
       </c>
       <c r="AI22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK22" t="n">
         <v>25</v>
       </c>
       <c r="AL22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM22" t="n">
         <v>20</v>
       </c>
       <c r="AN22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO22" t="n">
         <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AR22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AU22" t="n">
         <v>30</v>
@@ -4442,19 +4509,19 @@
         <v>19</v>
       </c>
       <c r="AY22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BB22" t="n">
         <v>12</v>
       </c>
       <c r="BC22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -4564,13 +4631,13 @@
         <v>1</v>
       </c>
       <c r="AE23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF23" t="n">
         <v>30</v>
       </c>
       <c r="AG23" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH23" t="n">
         <v>2</v>
@@ -4582,7 +4649,7 @@
         <v>2</v>
       </c>
       <c r="AK23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL23" t="n">
         <v>7</v>
@@ -4600,25 +4667,25 @@
         <v>29</v>
       </c>
       <c r="AQ23" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR23" t="n">
         <v>6</v>
       </c>
       <c r="AS23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AT23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU23" t="n">
         <v>17</v>
       </c>
       <c r="AV23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX23" t="n">
         <v>7</v>
@@ -4627,7 +4694,7 @@
         <v>28</v>
       </c>
       <c r="AZ23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA23" t="n">
         <v>26</v>
@@ -4636,7 +4703,7 @@
         <v>12</v>
       </c>
       <c r="BC23" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>4</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>2</v>
@@ -4758,16 +4825,16 @@
         <v>3</v>
       </c>
       <c r="AI24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK24" t="n">
         <v>2</v>
       </c>
       <c r="AL24" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM24" t="n">
         <v>15</v>
@@ -4776,28 +4843,28 @@
         <v>12</v>
       </c>
       <c r="AO24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AP24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR24" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AS24" t="n">
         <v>13</v>
       </c>
       <c r="AT24" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU24" t="n">
         <v>9</v>
       </c>
       <c r="AV24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW24" t="n">
         <v>1</v>
@@ -4812,13 +4879,13 @@
         <v>11</v>
       </c>
       <c r="BA24" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC24" t="n">
         <v>11</v>
-      </c>
-      <c r="BB24" t="n">
-        <v>5</v>
-      </c>
-      <c r="BC24" t="n">
-        <v>10</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>13</v>
       </c>
       <c r="AD25" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>2</v>
@@ -4940,7 +5007,7 @@
         <v>3</v>
       </c>
       <c r="AI25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AJ25" t="n">
         <v>10</v>
@@ -4949,7 +5016,7 @@
         <v>5</v>
       </c>
       <c r="AL25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM25" t="n">
         <v>20</v>
@@ -4964,43 +5031,43 @@
         <v>24</v>
       </c>
       <c r="AQ25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AS25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AU25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV25" t="n">
         <v>7</v>
       </c>
       <c r="AW25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX25" t="n">
         <v>13</v>
       </c>
       <c r="AY25" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA25" t="n">
         <v>30</v>
       </c>
       <c r="BB25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -5107,52 +5174,52 @@
         <v>-13</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG26" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH26" t="n">
         <v>3</v>
       </c>
       <c r="AI26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK26" t="n">
         <v>25</v>
       </c>
       <c r="AL26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO26" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ26" t="n">
         <v>18</v>
       </c>
       <c r="AR26" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AS26" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT26" t="n">
         <v>22</v>
@@ -5170,7 +5237,7 @@
         <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ26" t="n">
         <v>1</v>
@@ -5179,10 +5246,10 @@
         <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>2</v>
       </c>
       <c r="AD27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE27" t="n">
         <v>2</v>
@@ -5304,16 +5371,16 @@
         <v>3</v>
       </c>
       <c r="AI27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AK27" t="n">
         <v>25</v>
       </c>
       <c r="AL27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM27" t="n">
         <v>15</v>
@@ -5322,22 +5389,22 @@
         <v>12</v>
       </c>
       <c r="AO27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP27" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ27" t="n">
         <v>19</v>
       </c>
       <c r="AR27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AS27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AT27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU27" t="n">
         <v>29</v>
@@ -5346,10 +5413,10 @@
         <v>2</v>
       </c>
       <c r="AW27" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY27" t="n">
         <v>29</v>
@@ -5361,7 +5428,7 @@
         <v>18</v>
       </c>
       <c r="BB27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC27" t="n">
         <v>15</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>7</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5489,7 +5556,7 @@
         <v>8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK28" t="n">
         <v>4</v>
@@ -5507,19 +5574,19 @@
         <v>27</v>
       </c>
       <c r="AP28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ28" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
@@ -5537,7 +5604,7 @@
         <v>4</v>
       </c>
       <c r="AZ28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA28" t="n">
         <v>29</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>6</v>
       </c>
       <c r="AD29" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE29" t="n">
         <v>2</v>
@@ -5674,22 +5741,22 @@
         <v>6</v>
       </c>
       <c r="AK29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL29" t="n">
         <v>22</v>
       </c>
       <c r="AM29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AN29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO29" t="n">
         <v>26</v>
       </c>
       <c r="AP29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AQ29" t="n">
         <v>30</v>
@@ -5698,7 +5765,7 @@
         <v>1</v>
       </c>
       <c r="AS29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT29" t="n">
         <v>3</v>
@@ -5707,10 +5774,10 @@
         <v>26</v>
       </c>
       <c r="AV29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX29" t="n">
         <v>7</v>
@@ -5719,16 +5786,16 @@
         <v>24</v>
       </c>
       <c r="AZ29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC29" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -5835,16 +5902,16 @@
         <v>-3</v>
       </c>
       <c r="AD30" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG30" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH30" t="n">
         <v>3</v>
@@ -5856,31 +5923,31 @@
         <v>18</v>
       </c>
       <c r="AK30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL30" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AM30" t="n">
         <v>14</v>
       </c>
       <c r="AN30" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AP30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AQ30" t="n">
         <v>23</v>
       </c>
       <c r="AR30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT30" t="n">
         <v>10</v>
@@ -5889,7 +5956,7 @@
         <v>7</v>
       </c>
       <c r="AV30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AW30" t="n">
         <v>22</v>
@@ -5898,19 +5965,19 @@
         <v>13</v>
       </c>
       <c r="AY30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BA30" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB30" t="n">
         <v>15</v>
       </c>
       <c r="BC30" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
@@ -6017,34 +6084,34 @@
         <v>-11</v>
       </c>
       <c r="AD31" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AE31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AF31" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AG31" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH31" t="n">
         <v>3</v>
       </c>
       <c r="AI31" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL31" t="n">
         <v>6</v>
       </c>
       <c r="AM31" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AN31" t="n">
         <v>10</v>
@@ -6053,10 +6120,10 @@
         <v>5</v>
       </c>
       <c r="AP31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AQ31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6071,7 +6138,7 @@
         <v>13</v>
       </c>
       <c r="AV31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AW31" t="n">
         <v>25</v>
@@ -6080,19 +6147,19 @@
         <v>25</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
         <v>30</v>
       </c>
       <c r="BA31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BB31" t="n">
         <v>11</v>
       </c>
       <c r="BC31" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>10-31-2013-14</t>
+          <t>2013-10-31</t>
         </is>
       </c>
     </row>
